--- a/data/semi_structured/Investment_AI_Portfolio_Risk_Q2_2026.xlsx
+++ b/data/semi_structured/Investment_AI_Portfolio_Risk_Q2_2026.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Risk" sheetId="1" r:id="Re0ce33a806b94fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Risk" sheetId="1" r:id="R55feb80793d74c7a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -310,8 +310,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
@@ -348,10 +348,10 @@
     </x:row>
     <x:row r="2" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>IAGF</x:v>
+        <x:v>IA-FUND-01</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Investment AI Growth Fund</x:v>
+        <x:v>Synthetic Growth Fund 01</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>Growth Equity</x:v>
@@ -374,10 +374,10 @@
     </x:row>
     <x:row r="3" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A3" s="11" t="str">
-        <x:v>IACE</x:v>
+        <x:v>IA-FUND-02</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Investment AI Core Equity Fund</x:v>
+        <x:v>Synthetic Core Equity Fund 02</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>Core Equity</x:v>
@@ -400,10 +400,10 @@
     </x:row>
     <x:row r="4" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A4" s="11" t="str">
-        <x:v>IASO</x:v>
+        <x:v>IA-FUND-03</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Investment AI Sustainable Opportunities Fund</x:v>
+        <x:v>Synthetic Sustainable Fund 03</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>Sustainable Equity</x:v>
@@ -427,7 +427,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9682dabbb355486c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R879dc3df36064088"/>
   </x:tableParts>
 </x:worksheet>
 </file>